--- a/outputs/etf_trend_strategy/threshold_0.7/backtests/window_20/return_vol_r2/post_rank_positive_return/rebalance_1d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.7/backtests/window_20/return_vol_r2/post_rank_positive_return/rebalance_1d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
@@ -466,10 +466,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.09217477542140728</v>
+        <v>0.02640445452820495</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.2804666777983102</v>
+        <v>0.1627447131039174</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.441657337858894</v>
+        <v>0.1704875413814289</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.6555333990917158</v>
+        <v>0.2420912494293858</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2186823383750846</v>
+        <v>0.1297410790848365</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.479096354795966</v>
+        <v>0.2303746745979476</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>57.67324767055657</v>
+        <v>20.2434988775194</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.4024306902292815</v>
+        <v>-0.1347409264885939</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.252526278462895</v>
+        <v>0.2769509559769353</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-2.053601207242055</v>
+        <v>-0.4602661248769594</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-2.584252571357257</v>
+        <v>-0.660252395972185</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.4347119078554974</v>
+        <v>0.2154397500132645</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.9546792057774484</v>
+        <v>-0.6493699605397236</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>53.65944151030666</v>
+        <v>48.81569480190458</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.0787270480763268</v>
+        <v>-0.06726158157444706</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2194401228390067</v>
+        <v>0.2272515860973328</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.3474332103202971</v>
+        <v>-0.2710155660465492</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.4919015185232843</v>
+        <v>-0.3674838372853722</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2549228703178449</v>
+        <v>0.2224481839167423</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.3210515907878003</v>
+        <v>-0.3144169779680556</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>59.86837904571166</v>
+        <v>56.24165258824257</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.002396002551593113</v>
+        <v>0.07718888644436595</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2532024768437012</v>
+        <v>0.3529660388271971</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.0554991672118741</v>
+        <v>0.3520384650307272</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.08897354153808831</v>
+        <v>0.5270650824632139</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1787822721014378</v>
+        <v>0.2112864859494042</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.01395489208188897</v>
+        <v>0.3810165635595316</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>61.62902213221749</v>
+        <v>56.79964107259257</v>
       </c>
     </row>
     <row r="6">
@@ -636,25 +636,25 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.05928362124192432</v>
+        <v>-0.1689049075147334</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2346076683493935</v>
+        <v>0.2655310933107406</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.3092953666330171</v>
+        <v>-0.6444334708710761</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.4104210023831731</v>
+        <v>-0.8377790852284626</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.2128167736941765</v>
+        <v>0.3271611565841093</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.2891950494210901</v>
+        <v>-0.5336217883820095</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>68.14537327071433</v>
+        <v>66.6209939091126</v>
       </c>
     </row>
     <row r="7">
@@ -664,25 +664,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.1845723076485091</v>
+        <v>0.4951698511408404</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.291980114300701</v>
+        <v>0.3897618770873125</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.146659439582368</v>
+        <v>2.028189925888391</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.666137239914849</v>
+        <v>3.251427654355025</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.170246709710122</v>
+        <v>0.1397618096741073</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.111351257457857</v>
+        <v>7.680962602613103</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>56.9662542539643</v>
+        <v>50.31588937927297</v>
       </c>
     </row>
   </sheetData>
